--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2583,8 +2583,8 @@
       <c r="S19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
         <v>0</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U36" s="9" t="n">
         <v>0</v>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6759,8 +6759,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6909,13 +6909,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>6</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9833,8 +9833,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10960,8 +10960,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12077,8 +12077,8 @@
       <c r="S113" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
@@ -14590,7 +14590,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14660,8 +14660,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -21087,7 +21087,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21219,7 +21219,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -21417,7 +21417,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -21681,7 +21681,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -21780,7 +21780,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -21945,7 +21945,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -9127,7 +9131,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -10355,7 +10363,11 @@
       <c r="AB96" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -11482,7 +11494,11 @@
       <c r="AB107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -12310,7 +12326,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -15994,7 +16014,11 @@
       <c r="AB151" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16402,7 +16426,11 @@
       <c r="AB155" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC155" s="4" t="inlineStr"/>
+      <c r="AC155" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -16604,7 +16632,11 @@
       <c r="AB157" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC157" s="4" t="inlineStr"/>
+      <c r="AC157" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -17424,7 +17456,11 @@
       <c r="AB165" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC165" s="4" t="inlineStr"/>
+      <c r="AC165" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -18959,7 +18995,11 @@
       <c r="AB180" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC180" s="4" t="inlineStr"/>
+      <c r="AC180" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -20284,7 +20324,11 @@
       <c r="AB193" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC193" s="4" t="inlineStr"/>
+      <c r="AC193" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="9" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2205,8 +2205,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2979,8 +2979,8 @@
       <c r="S23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="9" t="n">
-        <v>0</v>
+      <c r="T23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U23" s="9" t="n">
         <v>0</v>
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3672,8 +3672,8 @@
       <c r="S30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="9" t="n">
-        <v>0</v>
+      <c r="T30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U30" s="9" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7898,8 +7898,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -9815,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11384,8 +11384,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11635,13 +11635,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -15949,13 +15949,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>4</v>
       </c>
       <c r="W151" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>6</v>
@@ -17583,7 +17583,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17635,8 +17635,8 @@
       <c r="S167" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T167" s="9" t="n">
-        <v>0</v>
+      <c r="T167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U167" s="9" t="n">
         <v>0</v>
@@ -18609,7 +18609,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18679,8 +18679,8 @@
       <c r="Y177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="9" t="n">
-        <v>0</v>
+      <c r="Z177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA177" s="10" t="n">
         <v>1</v>
@@ -18859,7 +18859,7 @@
         <v>0</v>
       </c>
       <c r="Q179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>0</v>
@@ -21131,7 +21131,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21164,7 +21164,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21527,7 +21527,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -22187,7 +22187,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>1</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="9" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="9" t="n">
         <v>0</v>
@@ -1512,8 +1512,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1809,8 +1809,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2106,8 +2106,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2304,8 +2304,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3096,8 +3096,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3789,8 +3789,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -3882,8 +3882,8 @@
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="9" t="n">
-        <v>3</v>
+      <c r="X32" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4581,8 +4581,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5373,8 +5373,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5746,7 +5746,7 @@
         <v>2</v>
       </c>
       <c r="R51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="9" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5868,8 +5868,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6660,8 +6660,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -6909,13 +6909,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>6</v>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7171,8 +7171,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7692,8 +7692,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8003,8 +8003,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="9" t="n">
         <v>0</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="X79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8866,13 +8866,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8922,8 +8922,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9635,8 +9635,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9946,8 +9946,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10029,8 +10029,8 @@
       <c r="S93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10148,8 +10148,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10179,7 +10179,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10249,8 +10249,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10459,8 +10459,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10669,8 +10669,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10871,8 +10871,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11691,8 +11691,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11901,8 +11901,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12729,8 +12729,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -13689,7 +13689,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13759,8 +13759,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14931,13 +14931,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -14987,8 +14987,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15018,7 +15018,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15088,8 +15088,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15290,8 +15290,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -16452,7 +16452,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16522,8 +16522,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q170" s="9" t="n">
         <v>0</v>
@@ -19163,7 +19163,7 @@
         </is>
       </c>
       <c r="P182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q182" s="9" t="n">
         <v>0</v>
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19383,8 +19383,8 @@
       <c r="T184" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U184" s="9" t="n">
-        <v>0</v>
+      <c r="U184" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V184" s="9" t="n">
         <v>0</v>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19583,8 +19583,8 @@
       <c r="R186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S186" s="9" t="n">
-        <v>1</v>
+      <c r="S186" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T186" s="9" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20420,8 +20420,8 @@
       <c r="Y194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" s="9" t="n">
-        <v>0</v>
+      <c r="Z194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA194" s="10" t="n">
         <v>1</v>
@@ -20552,7 +20552,7 @@
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20622,8 +20622,8 @@
       <c r="Y196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z196" s="9" t="n">
-        <v>0</v>
+      <c r="Z196" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA196" s="10" t="n">
         <v>1</v>
@@ -21065,7 +21065,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21131,7 +21131,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21197,7 +21197,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21296,7 +21296,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -21395,7 +21395,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -21527,7 +21527,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21593,7 +21593,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -21659,7 +21659,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -21692,7 +21692,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21725,7 +21725,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -21791,7 +21791,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -21824,7 +21824,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -21857,7 +21857,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21956,7 +21956,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22022,7 +22022,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22055,7 +22055,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22121,7 +22121,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22319,7 +22319,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -22352,7 +22352,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -22385,7 +22385,7 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -22418,7 +22418,7 @@
         <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1159,13 +1159,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1395,14 +1395,14 @@
       <c r="S7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1599,8 +1599,8 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>7</v>
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2149,17 +2149,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2248,17 +2248,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2886,8 +2886,8 @@
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>3</v>
+      <c r="V22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>4</v>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3337,17 +3337,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3535,13 +3535,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3733,17 +3733,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3777,11 +3777,11 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" s="9" t="n">
-        <v>0</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W31" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>6</v>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4030,13 +4030,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4129,13 +4129,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4371,11 +4371,11 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>1</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>6</v>
@@ -4426,13 +4426,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4624,13 +4624,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="10" t="n">
         <v>1</v>
@@ -4822,17 +4822,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5119,17 +5119,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5515,17 +5515,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>7</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6109,13 +6109,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="9" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6406,13 +6406,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6604,17 +6604,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6703,13 +6703,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6804,17 +6804,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6909,13 +6909,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6956,8 +6956,8 @@
       <c r="V63" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W63" s="9" t="n">
-        <v>2</v>
+      <c r="W63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>6</v>
@@ -7014,13 +7014,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7115,13 +7115,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7220,17 +7220,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7325,13 +7325,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7531,13 +7531,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7636,13 +7636,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7737,17 +7737,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7842,17 +7842,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -7947,13 +7947,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8048,13 +8048,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8254,13 +8254,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8359,17 +8359,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8397,8 +8397,8 @@
       <c r="S77" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>4</v>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8464,17 +8464,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8499,8 +8499,8 @@
       <c r="R78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S78" s="9" t="n">
-        <v>1</v>
+      <c r="S78" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8569,13 +8569,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8616,8 +8616,8 @@
       <c r="V79" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W79" s="9" t="n">
-        <v>1</v>
+      <c r="W79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X79" s="9" t="n">
         <v>3</v>
@@ -8668,13 +8668,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8767,17 +8767,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8866,13 +8866,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8965,13 +8965,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9066,13 +9066,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>7</v>
@@ -9171,13 +9171,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9316,11 +9316,11 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>3</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="9" t="n">
         <v>1</v>
@@ -9373,13 +9373,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9579,13 +9579,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9680,17 +9680,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9725,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9785,17 +9785,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -9890,13 +9890,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9991,13 +9991,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10020,8 +10020,8 @@
       <c r="P93" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q93" s="9" t="n">
-        <v>1</v>
+      <c r="Q93" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -10092,13 +10092,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>6</v>
+        <v>-12</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10403,17 +10403,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10508,17 +10508,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10714,13 +10714,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10815,13 +10815,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11021,13 +11021,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11223,13 +11223,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11328,13 +11328,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11429,13 +11429,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11477,7 +11477,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -11534,13 +11534,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11635,13 +11635,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11740,13 +11740,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11950,13 +11950,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12055,13 +12055,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12160,13 +12160,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12261,13 +12261,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12366,13 +12366,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12673,13 +12673,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12714,8 +12714,8 @@
       <c r="T119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
+      <c r="U119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V119" s="9" t="n">
         <v>0</v>
@@ -12774,13 +12774,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12875,13 +12875,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12980,17 +12980,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -13186,17 +13186,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13231,7 +13231,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13287,13 +13287,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13388,17 +13388,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13493,17 +13493,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13598,13 +13598,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13808,17 +13808,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -14010,13 +14010,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14115,13 +14115,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14216,13 +14216,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14317,17 +14317,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14418,17 +14418,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14466,7 +14466,7 @@
         <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>6</v>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14729,17 +14729,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14830,13 +14830,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14931,13 +14931,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -15032,13 +15032,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15234,17 +15234,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15436,13 +15436,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -15480,8 +15480,8 @@
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="9" t="n">
-        <v>3</v>
+      <c r="V146" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15541,17 +15541,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
@@ -15646,13 +15646,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15747,13 +15747,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15949,13 +15949,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16054,17 +16054,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="8" t="n">
@@ -16098,11 +16098,11 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>1</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X152" s="9" t="n">
         <v>3</v>
@@ -16159,13 +16159,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16260,13 +16260,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -16361,13 +16361,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="9" t="n">
         <v>0</v>
@@ -16409,7 +16409,7 @@
         <v>4</v>
       </c>
       <c r="W155" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X155" s="10" t="n">
         <v>4</v>
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16567,13 +16567,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16609,13 +16609,13 @@
         <v>1</v>
       </c>
       <c r="U157" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V157" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="V157" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X157" s="10" t="n">
         <v>6</v>
@@ -16672,13 +16672,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16773,17 +16773,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -16911,7 +16911,7 @@
         <v>2</v>
       </c>
       <c r="R160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S160" s="9" t="n">
         <v>0</v>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16983,13 +16983,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17021,14 +17021,14 @@
       <c r="S161" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U161" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -17185,17 +17185,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -17290,17 +17290,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="8" t="n">
@@ -17391,13 +17391,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17597,17 +17597,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L167" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -17702,17 +17702,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L168" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M168" s="8" t="n">
@@ -17803,17 +17803,17 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L169" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L169" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M169" s="8" t="n">
@@ -17851,7 +17851,7 @@
         <v>4</v>
       </c>
       <c r="W169" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X169" s="9" t="n">
         <v>3</v>
@@ -17908,17 +17908,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L170" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M170" s="8" t="n">
@@ -18013,13 +18013,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18159,7 +18159,7 @@
         <v>0</v>
       </c>
       <c r="V172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -18316,17 +18316,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L174" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -18421,13 +18421,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18522,13 +18522,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -18623,13 +18623,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>0</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -18829,13 +18829,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18930,17 +18930,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
@@ -19035,13 +19035,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -19136,13 +19136,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19237,17 +19237,17 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M183" s="8" t="n">
@@ -19267,7 +19267,7 @@
         <v>0</v>
       </c>
       <c r="Q183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>0</v>
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19447,13 +19447,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -19488,8 +19488,8 @@
       <c r="T185" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U185" s="9" t="n">
-        <v>0</v>
+      <c r="U185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V185" s="9" t="n">
         <v>0</v>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19548,17 +19548,17 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L186" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L186" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M186" s="8" t="n">
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q186" s="9" t="n">
         <v>1</v>
@@ -19592,11 +19592,11 @@
       <c r="U186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V186" s="9" t="n">
-        <v>3</v>
+      <c r="V186" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W186" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X186" s="10" t="n">
         <v>6</v>
@@ -19754,13 +19754,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -19855,13 +19855,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -19956,13 +19956,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -20057,13 +20057,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20158,13 +20158,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -20259,13 +20259,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
@@ -20303,11 +20303,11 @@
       <c r="U193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V193" s="9" t="n">
+      <c r="V193" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W193" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W193" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X193" s="10" t="n">
         <v>7</v>
@@ -20364,13 +20364,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -20465,17 +20465,17 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L195" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M195" s="8" t="n">
@@ -20510,7 +20510,7 @@
         <v>0</v>
       </c>
       <c r="V195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W195" s="9" t="n">
         <v>0</v>
@@ -20566,17 +20566,17 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L196" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M196" s="8" t="n">
@@ -20611,7 +20611,7 @@
         <v>0</v>
       </c>
       <c r="V196" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W196" s="9" t="n">
         <v>0</v>
@@ -20671,17 +20671,17 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M197" s="8" t="n">
@@ -20776,13 +20776,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -20877,13 +20877,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21146,7 +21146,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21164,7 +21164,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21212,7 +21212,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -21230,7 +21230,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21245,7 +21245,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -21263,7 +21263,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -21344,7 +21344,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -21377,7 +21377,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -21443,7 +21443,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -21461,7 +21461,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -21476,7 +21476,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -21542,7 +21542,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -21560,7 +21560,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21575,7 +21575,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -21593,7 +21593,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -21608,7 +21608,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -21626,7 +21626,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21674,7 +21674,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -21692,7 +21692,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21707,7 +21707,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -21740,7 +21740,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -21857,7 +21857,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21905,7 +21905,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -21971,7 +21971,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -22004,7 +22004,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -22037,7 +22037,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -22055,7 +22055,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22070,7 +22070,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -22088,7 +22088,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22103,7 +22103,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -22121,13 +22121,13 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -22154,7 +22154,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -22169,7 +22169,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -22202,7 +22202,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -22235,7 +22235,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -22268,7 +22268,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -22301,7 +22301,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -22319,7 +22319,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -22334,7 +22334,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -22352,7 +22352,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -22367,7 +22367,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -22385,7 +22385,7 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -22433,7 +22433,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -900,8 +900,8 @@
       <c r="S2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="9" t="n">
-        <v>0</v>
+      <c r="T2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="9" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -3733,13 +3733,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>4</v>
       </c>
       <c r="W31" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>6</v>
@@ -4129,13 +4129,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4624,13 +4624,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>7</v>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4851,8 +4851,8 @@
       <c r="P42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>1</v>
+      <c r="Q42" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6909,13 +6909,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>6</v>
@@ -7636,13 +7636,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -8254,13 +8254,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8359,13 +8359,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8668,13 +8668,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10508,13 +10508,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10815,13 +10815,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
@@ -11223,13 +11223,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -13388,17 +13388,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13433,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13493,13 +13493,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -14317,13 +14317,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -16773,13 +16773,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>1</v>
       </c>
       <c r="S160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" s="9" t="n">
         <v>0</v>
@@ -17013,7 +17013,7 @@
         <v>1</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
@@ -17185,13 +17185,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -17597,17 +17597,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L167" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -18114,13 +18114,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>1</v>
@@ -18159,7 +18159,7 @@
         <v>0</v>
       </c>
       <c r="V172" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -18522,13 +18522,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18867,8 +18867,8 @@
       <c r="S179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T179" s="9" t="n">
-        <v>0</v>
+      <c r="T179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U179" s="9" t="n">
         <v>0</v>
@@ -18930,13 +18930,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -19237,13 +19237,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="P186" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q186" s="9" t="n">
         <v>1</v>
@@ -19584,7 +19584,7 @@
         <v>0</v>
       </c>
       <c r="S186" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T186" s="9" t="n">
         <v>0</v>
@@ -20259,13 +20259,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
@@ -20364,13 +20364,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -20877,13 +20877,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>0</v>
       </c>
       <c r="V199" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W199" s="9" t="n">
         <v>0</v>
@@ -21032,7 +21032,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -22202,7 +22202,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -22286,7 +22286,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>

--- a/docs/d/31/inyear.xlsx
+++ b/docs/d/31/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 25 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 25 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>1</v>
@@ -903,8 +903,8 @@
       <c r="T2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U2" s="9" t="n">
-        <v>0</v>
+      <c r="U2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V2" s="9" t="n">
         <v>2</v>
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-18</v>
+        <v>-15</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2586,8 +2586,8 @@
       <c r="T19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U19" s="9" t="n">
-        <v>0</v>
+      <c r="U19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>0</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>4</v>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3375,11 +3375,11 @@
       <c r="S27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V27" s="10" t="n">
         <v>4</v>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>1</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3733,13 +3733,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>4</v>
       </c>
       <c r="W31" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>6</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4528,10 +4528,10 @@
         <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>0</v>
@@ -5119,13 +5119,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6109,13 +6109,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6211,10 +6211,10 @@
         <v>15</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6604,13 +6604,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6703,13 +6703,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6747,11 +6747,11 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>1</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>5</v>
@@ -6909,13 +6909,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -6957,7 +6957,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>6</v>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8359,13 +8359,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -8406,8 +8406,8 @@
       <c r="V77" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W77" s="9" t="n">
-        <v>3</v>
+      <c r="W77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>4</v>
@@ -9066,13 +9066,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9680,17 +9680,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9725,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9991,13 +9991,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10327,8 +10327,8 @@
       <c r="P96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" s="9" t="n">
-        <v>1</v>
+      <c r="Q96" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -11534,13 +11534,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11635,13 +11635,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12055,13 +12055,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12102,8 +12102,8 @@
       <c r="V113" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W113" s="9" t="n">
-        <v>2</v>
+      <c r="W113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>4</v>
@@ -12160,13 +12160,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12366,13 +12366,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>1</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -12861,7 +12861,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12913,8 +12913,8 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13224,8 +13224,8 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13598,13 +13598,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13642,8 +13642,8 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>3</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13730,7 +13730,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -14958,7 +14958,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -16054,13 +16054,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16567,13 +16567,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="U157" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V157" s="10" t="n">
         <v>4</v>
@@ -17185,13 +17185,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17908,13 +17908,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>0</v>
       </c>
       <c r="S180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T180" s="10" t="n">
         <v>1</v>
@@ -20259,13 +20259,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
@@ -20364,13 +20364,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21131,7 +21131,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21197,7 +21197,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -21461,7 +21461,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -21560,7 +21560,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21674,7 +21674,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -21692,7 +21692,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21824,7 +21824,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -21890,7 +21890,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -21923,7 +21923,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
